--- a/Form-Layout/ImportLayouts/Config/RPT_Import_Map.xlsx
+++ b/Form-Layout/ImportLayouts/Config/RPT_Import_Map.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Film\GIT\SDA\Form-Layout\ImportLayouts\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SBO_Warit\Form-Layout\ImportLayouts\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAEBB9EF-BBBF-41CE-9969-E878E9DA3996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87787DE-2E36-46E3-A08B-E61C1993F1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{014D90F8-196E-40BF-BFE8-06F39FDF4BE1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{014D90F8-196E-40BF-BFE8-06F39FDF4BE1}"/>
   </bookViews>
   <sheets>
     <sheet name="RPT_MAP" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="425">
   <si>
     <t>No</t>
   </si>
@@ -99,9 +99,6 @@
     <t>Sales - AR</t>
   </si>
   <si>
-    <t>2. Sales - AR\1. Sales Quotation\1.Sale Quotation_ใบเสนอราคาขาย(BOM)</t>
-  </si>
-  <si>
     <t>Sales Quotation</t>
   </si>
   <si>
@@ -111,18 +108,6 @@
     <t>QUT1</t>
   </si>
   <si>
-    <t>Sales Quotation (BOM) - SDA</t>
-  </si>
-  <si>
-    <t>รองรับ BOM</t>
-  </si>
-  <si>
-    <t>Sales Quotation (BOM) EN - SDA</t>
-  </si>
-  <si>
-    <t>ภาษาอังกฤษ BOM</t>
-  </si>
-  <si>
     <t>1.Sale Quotation_ใบเสนอราคาขาย_(Dis).rpt</t>
   </si>
   <si>
@@ -156,15 +141,6 @@
     <t>Sales Order (Dis) - SDA</t>
   </si>
   <si>
-    <t>1.Sale Order_ใบสั่งขาย_(Bom).rpt</t>
-  </si>
-  <si>
-    <t>2. Sales - AR\2. Sales Order\3.Sale Order_ใบสั่งขาย_(Bomm)</t>
-  </si>
-  <si>
-    <t>Sales Order (BOM) - SDA</t>
-  </si>
-  <si>
     <t>2.Delivery_ใบส่งของ_(Batch_Serial).rpt</t>
   </si>
   <si>
@@ -1083,12 +1059,6 @@
     <t>1.Retrun_ใบรับคืนสินค้า_(Batch_Serial).rpt</t>
   </si>
   <si>
-    <t>2.Sale Quotation_ใบเสนอราคาขาย_(BOM) ENG.rpt</t>
-  </si>
-  <si>
-    <t>2.Sale Quotation_ใบเสนอราคาขาย_(Bom).rpt</t>
-  </si>
-  <si>
     <t>1.Sale Quotation_ใบเสนอราคาขาย_(Dis) ENG.rpt</t>
   </si>
   <si>
@@ -1101,45 +1071,18 @@
     <t>Batch/Serial + ภาษาอังกฤษ</t>
   </si>
   <si>
-    <t>1.AR Down Payment_BOM ใบเสร็จรับเงินมัดจำ.rpt</t>
-  </si>
-  <si>
-    <t>AR DP (BOM) - SDA</t>
-  </si>
-  <si>
-    <t>1.AR Down Payment_BOM_ENG ใบเสร็จรับเงินมัดจำ.rpt</t>
-  </si>
-  <si>
-    <t>AR DP (BOM) EN - SDA</t>
-  </si>
-  <si>
-    <t>รองรับ BOM + ภาษาอังกฤษ</t>
-  </si>
-  <si>
     <t>1.AR Down Payment_ENG ใบเสร็จรับเงินมัดจำ.rpt</t>
   </si>
   <si>
     <t>AR DP EN - SDA</t>
   </si>
   <si>
-    <t>2.AR Down PaymentTax Invoice_BOM ใบเสร็จรับเงินมัดจำใบกำกับภาษี.rpt</t>
-  </si>
-  <si>
-    <t>2.AR Down PaymentTax Invoice_BOM_ENG ใบเสร็จรับเงินมัดจำใบกำกับภาษี.rpt</t>
-  </si>
-  <si>
     <t>2.AR Down PaymentTax Invoice_ENG ใบเสร็จรับเงินมัดจำใบกำกับภาษี.rpt</t>
   </si>
   <si>
-    <t>3.AR Down Payment Invoice_BOM ใบแจ้งหนี้เงินค่ามัดจำใบกำกับภาษี.rpt</t>
-  </si>
-  <si>
     <t>2. Sales - AR\5. AR Down Payment Invoice\3.AR Down Payment Invoice_ใบแจ้งหนี้เงินค่ามัดจำใบกำกับภาษี</t>
   </si>
   <si>
-    <t>3.AR Down PaymentTax Invoice_BOM_ENG ใบแจ้งหนี้เงินค่ามัดจำใบกำกับภาษี.rpt</t>
-  </si>
-  <si>
     <t>3.AR Down PaymentTax Invoice_ENG ใบแจ้งหนี้เงินค่ามัดจำใบกำกับภาษี.rpt</t>
   </si>
   <si>
@@ -1149,21 +1092,6 @@
     <t>AR Down PaymentTax Invoice_ใบแจ้งหนี้เงินค่ามัดจำใบกำกับภาษี</t>
   </si>
   <si>
-    <t>1.AR Invoice_BOM ใบแจ้งหนี้.rpt</t>
-  </si>
-  <si>
-    <t>2. Sales - AR\6. AR Invoice\1 AR Invoice_TH (Bom)</t>
-  </si>
-  <si>
-    <t>AR Invoice (BOM) - SDA</t>
-  </si>
-  <si>
-    <t>1.AR Invoice_BOM_ENG ใบแจ้งหนี้.rpt</t>
-  </si>
-  <si>
-    <t>AR Invoice (BOM) EN - SDA</t>
-  </si>
-  <si>
     <t>2.AR Invoice_ENG ใบแจ้งหนี้_(Dis).rpt</t>
   </si>
   <si>
@@ -1182,15 +1110,6 @@
     <t>AR Invoice (Dis) - SDA</t>
   </si>
   <si>
-    <t>3.BillingAR InvoiceTax Invoice_ENG ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี (Bom).rpt</t>
-  </si>
-  <si>
-    <t>2. Sales - AR\6. AR Invoice\3.BillingAR InvoiceTax Invoice_ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี (Bom)</t>
-  </si>
-  <si>
-    <t>3.BillingAR InvoiceTax Invoice_ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี (Bom).rpt</t>
-  </si>
-  <si>
     <t>4.BillingAR InvoiceTax Invoice_ENG ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี (Dis).rpt</t>
   </si>
   <si>
@@ -1198,15 +1117,6 @@
   </si>
   <si>
     <t>4.BillingAR InvoiceTax Invoice_ใบวางบิลใบแจ้งหนี้ใบกำกับภาษี (Dis).rpt</t>
-  </si>
-  <si>
-    <t>5.BillingAR Invoice_ENG ใบวางบิลใบแจ้งหนี้ (Bom).rpt</t>
-  </si>
-  <si>
-    <t>2. Sales - AR\6. AR Invoice\5.BillingAR Invoice_ใบวางบิลใบแจ้งหนี้ (Bom)</t>
-  </si>
-  <si>
-    <t>5.BillingAR Invoice_ใบวางบิลใบแจ้งหนี้ (Bom).rpt</t>
   </si>
   <si>
     <t>6.BillingAR Invoice_ENG ใบวางบิลใบแจ้งหนี้ (Dis).rpt</t>
@@ -1869,7 +1779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F62795C-81CC-4DF6-8643-8C6776741771}">
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.69921875" customWidth="1"/>
@@ -1955,25 +1865,25 @@
     </row>
     <row r="3" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A3" s="12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>349</v>
+        <v>23</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="8" t="s">
         <v>22</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>23</v>
       </c>
       <c r="H3" s="3">
         <v>23</v>
@@ -1982,33 +1892,33 @@
         <v>149</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="7" t="s">
         <v>22</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>23</v>
       </c>
       <c r="H4" s="4">
         <v>23</v>
@@ -2017,1538 +1927,1538 @@
         <v>149</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>338</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H5" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I5" s="3">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="4">
-        <v>23</v>
-      </c>
-      <c r="I6" s="4">
-        <v>149</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>33</v>
+      <c r="C6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="3">
+        <v>15</v>
+      </c>
+      <c r="I6" s="3">
+        <v>140</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="11">
+        <v>9</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="C7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="E7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="F7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="3">
-        <v>17</v>
-      </c>
-      <c r="I7" s="3">
-        <v>139</v>
-      </c>
-      <c r="J7" s="3" t="s">
+      <c r="G7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>31</v>
+      <c r="H7" s="4">
+        <v>15</v>
+      </c>
+      <c r="I7" s="4">
+        <v>140</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="A8" s="12">
+        <v>10</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="C8" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="3">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3">
+        <v>141</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="4">
-        <v>17</v>
-      </c>
-      <c r="I8" s="4">
-        <v>139</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
+    </row>
+    <row r="9" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A9" s="11">
+        <v>11</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="3">
-        <v>15</v>
-      </c>
-      <c r="I9" s="3">
-        <v>140</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="C9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="4">
+        <v>203</v>
+      </c>
+      <c r="I9" s="4">
+        <v>65300</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <v>12</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="4">
-        <v>15</v>
-      </c>
-      <c r="I10" s="4">
-        <v>140</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="K10" s="4" t="s">
+      <c r="C10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="3">
+        <v>203</v>
+      </c>
+      <c r="I10" s="3">
+        <v>65300</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A11" s="12">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" s="3">
-        <v>16</v>
-      </c>
-      <c r="I11" s="3">
-        <v>141</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>48</v>
+      <c r="C11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="4">
+        <v>14</v>
+      </c>
+      <c r="I11" s="4">
+        <v>179</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>57</v>
+        <v>380</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H12" s="4">
-        <v>203</v>
+        <v>14</v>
       </c>
       <c r="I12" s="4">
-        <v>65300</v>
+        <v>179</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13" s="3">
-        <v>203</v>
-      </c>
-      <c r="I13" s="3">
-        <v>65300</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>67</v>
+        <v>15</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1470000113</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1470000113</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H14" s="4">
-        <v>14</v>
-      </c>
-      <c r="I14" s="4">
-        <v>179</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>78</v>
+      <c r="C14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="3">
+        <v>540000405</v>
+      </c>
+      <c r="I14" s="3">
+        <v>540000405</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>410</v>
+        <v>89</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="H15" s="4">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I15" s="4">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="H16" s="4">
-        <v>1470000113</v>
-      </c>
-      <c r="I16" s="4">
-        <v>1470000113</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>89</v>
+        <v>18</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H16" s="3">
+        <v>20</v>
+      </c>
+      <c r="I16" s="3">
+        <v>143</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A17" s="12">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H17" s="3">
-        <v>540000405</v>
-      </c>
-      <c r="I17" s="3">
-        <v>540000405</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>96</v>
+        <v>19</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" s="4">
+        <v>21</v>
+      </c>
+      <c r="I17" s="4">
+        <v>144</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="H18" s="4">
-        <v>22</v>
-      </c>
-      <c r="I18" s="4">
-        <v>142</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>103</v>
+        <v>20</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="H18" s="3">
+        <v>204</v>
+      </c>
+      <c r="I18" s="3">
+        <v>65301</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A19" s="12">
+        <v>21</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="H19" s="3">
-        <v>20</v>
-      </c>
-      <c r="I19" s="3">
-        <v>143</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>110</v>
+      <c r="I19" s="4">
+        <v>141</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
+        <v>22</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" s="4">
+        <v>18</v>
+      </c>
+      <c r="I20" s="4">
+        <v>141</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="11">
+        <v>23</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H21" s="3">
+        <v>18</v>
+      </c>
+      <c r="I21" s="3">
+        <v>141</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <v>24</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="H22" s="4">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="H20" s="4">
-        <v>21</v>
-      </c>
-      <c r="I20" s="4">
-        <v>144</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="H21" s="3">
-        <v>204</v>
-      </c>
-      <c r="I21" s="3">
-        <v>65301</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
-        <v>21</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="H22" s="4">
-        <v>18</v>
-      </c>
       <c r="I22" s="4">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A23" s="12">
-        <v>22</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="H23" s="4">
-        <v>18</v>
-      </c>
-      <c r="I23" s="4">
+        <v>25</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="J23" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G23" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="H23" s="3">
+        <v>69</v>
+      </c>
+      <c r="I23" s="3">
+        <v>992</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H24" s="3">
-        <v>18</v>
-      </c>
-      <c r="I24" s="3">
-        <v>141</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H24" s="4">
+        <v>24</v>
+      </c>
+      <c r="I24" s="4">
+        <v>170</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A25" s="12">
+        <v>27</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="H25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="H25" s="4">
-        <v>19</v>
-      </c>
-      <c r="I25" s="4">
-        <v>181</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>145</v>
+      <c r="I25" s="3">
+        <v>170</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="H26" s="3">
-        <v>69</v>
-      </c>
-      <c r="I26" s="3">
-        <v>992</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>152</v>
+        <v>28</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="H26" s="4">
+        <v>46</v>
+      </c>
+      <c r="I26" s="4">
+        <v>171</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>26</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="H27" s="4">
-        <v>24</v>
-      </c>
-      <c r="I27" s="4">
+        <v>29</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="H27" s="3">
+        <v>59</v>
+      </c>
+      <c r="I27" s="3">
+        <v>720</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="H28" s="3">
-        <v>24</v>
-      </c>
-      <c r="I28" s="3">
-        <v>170</v>
-      </c>
-      <c r="J28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="K28" s="3" t="s">
-        <v>131</v>
+      <c r="C28" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="H28" s="4">
+        <v>60</v>
+      </c>
+      <c r="I28" s="4">
+        <v>721</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A29" s="12">
-        <v>28</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="H29" s="4">
-        <v>46</v>
-      </c>
-      <c r="I29" s="4">
-        <v>171</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>170</v>
+        <v>31</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="H29" s="3">
+        <v>1250000001</v>
+      </c>
+      <c r="I29" s="3">
+        <v>1250000001</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="H30" s="3">
-        <v>59</v>
-      </c>
-      <c r="I30" s="3">
-        <v>720</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>178</v>
+        <v>32</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="H30" s="4">
+        <v>67</v>
+      </c>
+      <c r="I30" s="4">
+        <v>940</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
-        <v>30</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H31" s="4">
-        <v>60</v>
-      </c>
-      <c r="I31" s="4">
-        <v>721</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>185</v>
+        <v>33</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H31" s="3">
+        <v>1470000065</v>
+      </c>
+      <c r="I31" s="3">
+        <v>1470000065</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A32" s="12">
-        <v>31</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="H32" s="3">
-        <v>1250000001</v>
-      </c>
-      <c r="I32" s="3">
-        <v>1250000001</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>192</v>
+        <v>34</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="H32" s="4">
+        <v>1470000065</v>
+      </c>
+      <c r="I32" s="4">
+        <v>1470000065</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>32</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="H33" s="4">
-        <v>67</v>
-      </c>
-      <c r="I33" s="4">
-        <v>940</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>198</v>
+        <v>35</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="H33" s="3">
+        <v>162</v>
+      </c>
+      <c r="I33" s="3">
+        <v>184</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A34" s="12">
-        <v>33</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F34" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="H34" s="4">
+        <v>162</v>
+      </c>
+      <c r="I34" s="4">
+        <v>184</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="12">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="H35" s="3">
         <v>202</v>
       </c>
-      <c r="G34" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="H34" s="3">
-        <v>1470000065</v>
-      </c>
-      <c r="I34" s="3">
-        <v>1470000065</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A35" s="12">
-        <v>34</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="H35" s="4">
-        <v>1470000065</v>
-      </c>
-      <c r="I35" s="4">
-        <v>1470000065</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>209</v>
+      <c r="I35" s="3">
+        <v>65209</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>35</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="G36" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="H36" s="3">
-        <v>162</v>
-      </c>
-      <c r="I36" s="3">
-        <v>184</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>216</v>
+      <c r="C36" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="H36" s="4">
+        <v>59</v>
+      </c>
+      <c r="I36" s="4">
+        <v>720</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A37" s="12">
-        <v>36</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="F37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="G37" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="H37" s="4">
-        <v>162</v>
-      </c>
-      <c r="I37" s="4">
-        <v>184</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K37" s="4" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C37" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="H37" s="3">
+        <v>59</v>
+      </c>
+      <c r="I37" s="3">
+        <v>720</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A38" s="12">
-        <v>37</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="H38" s="3">
-        <v>202</v>
-      </c>
-      <c r="I38" s="3">
-        <v>65209</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>228</v>
+        <v>40</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="H38" s="4">
+        <v>60</v>
+      </c>
+      <c r="I38" s="4">
+        <v>721</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>38</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="F39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="G39" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="G39" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="H39" s="4">
-        <v>59</v>
-      </c>
-      <c r="I39" s="4">
-        <v>720</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="H39" s="3">
+        <v>60</v>
+      </c>
+      <c r="I39" s="3">
+        <v>721</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
-        <v>39</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="H40" s="3">
-        <v>59</v>
-      </c>
-      <c r="I40" s="3">
-        <v>720</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
-        <v>40</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="D41" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H41" s="4">
-        <v>60</v>
-      </c>
-      <c r="I41" s="4">
-        <v>721</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="C41" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C42" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="F42" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="G42" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="H42" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="H42" s="3">
-        <v>60</v>
-      </c>
-      <c r="I42" s="3">
-        <v>721</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>246</v>
+      <c r="I42" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
-        <v>42</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>254</v>
+        <v>45</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="12">
+      <c r="A44">
+        <v>46</v>
+      </c>
+      <c r="B44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" t="s">
+        <v>341</v>
+      </c>
+      <c r="D44" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44" t="s">
+        <v>46</v>
+      </c>
+      <c r="G44" t="s">
+        <v>47</v>
+      </c>
+      <c r="H44">
+        <v>16</v>
+      </c>
+      <c r="I44">
+        <v>141</v>
+      </c>
+      <c r="J44" t="s">
+        <v>342</v>
+      </c>
+      <c r="K44" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>49</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" t="s">
+        <v>344</v>
+      </c>
+      <c r="D45" t="s">
+        <v>50</v>
+      </c>
+      <c r="E45" t="s">
+        <v>51</v>
+      </c>
+      <c r="F45" t="s">
+        <v>52</v>
+      </c>
+      <c r="G45" t="s">
+        <v>53</v>
+      </c>
+      <c r="H45">
+        <v>203</v>
+      </c>
+      <c r="I45">
+        <v>65300</v>
+      </c>
+      <c r="J45" t="s">
+        <v>345</v>
+      </c>
+      <c r="K45" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="11">
-        <v>44</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>265</v>
-      </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="12">
-        <v>45</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>271</v>
+      <c r="A46">
+        <v>52</v>
+      </c>
+      <c r="B46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" t="s">
+        <v>346</v>
+      </c>
+      <c r="D46" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46" t="s">
+        <v>51</v>
+      </c>
+      <c r="F46" t="s">
+        <v>52</v>
+      </c>
+      <c r="G46" t="s">
+        <v>53</v>
+      </c>
+      <c r="H46">
+        <v>203</v>
+      </c>
+      <c r="I46">
+        <v>65300</v>
+      </c>
+      <c r="J46" t="s">
+        <v>345</v>
+      </c>
+      <c r="K46" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B47" t="s">
         <v>19</v>
       </c>
       <c r="C47" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D47" t="s">
+        <v>347</v>
+      </c>
+      <c r="E47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F47" t="s">
         <v>52</v>
       </c>
-      <c r="E47" t="s">
+      <c r="G47" t="s">
         <v>53</v>
       </c>
-      <c r="F47" t="s">
-        <v>54</v>
-      </c>
-      <c r="G47" t="s">
-        <v>55</v>
-      </c>
       <c r="H47">
-        <v>16</v>
+        <v>203</v>
       </c>
       <c r="I47">
-        <v>141</v>
+        <v>65300</v>
       </c>
       <c r="J47" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="K47" t="s">
-        <v>353</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B48" t="s">
         <v>19</v>
       </c>
       <c r="C48" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D48" t="s">
-        <v>58</v>
+        <v>347</v>
       </c>
       <c r="E48" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F48" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G48" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="H48">
         <v>203</v>
@@ -3557,260 +3467,260 @@
         <v>65300</v>
       </c>
       <c r="J48" t="s">
-        <v>355</v>
+        <v>54</v>
       </c>
       <c r="K48" t="s">
-        <v>25</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B49" t="s">
         <v>19</v>
       </c>
       <c r="C49" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D49" t="s">
-        <v>58</v>
+        <v>352</v>
       </c>
       <c r="E49" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F49" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H49">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="I49">
-        <v>65300</v>
+        <v>133</v>
       </c>
       <c r="J49" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="K49" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B50" t="s">
         <v>19</v>
       </c>
       <c r="C50" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D50" t="s">
-        <v>58</v>
+        <v>352</v>
       </c>
       <c r="E50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H50">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="I50">
-        <v>65300</v>
+        <v>133</v>
       </c>
       <c r="J50" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="K50" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B51" t="s">
         <v>19</v>
       </c>
       <c r="C51" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D51" t="s">
-        <v>65</v>
+        <v>358</v>
       </c>
       <c r="E51" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F51" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G51" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H51">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="I51">
-        <v>65300</v>
+        <v>133</v>
       </c>
       <c r="J51" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="K51" t="s">
-        <v>25</v>
+        <v>354</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="B52" t="s">
         <v>19</v>
       </c>
       <c r="C52" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D52" t="s">
-        <v>65</v>
+        <v>358</v>
       </c>
       <c r="E52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F52" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G52" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H52">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="I52">
-        <v>65300</v>
+        <v>133</v>
       </c>
       <c r="J52" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K52" t="s">
-        <v>358</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B53" t="s">
         <v>19</v>
       </c>
       <c r="C53" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D53" t="s">
-        <v>65</v>
+        <v>361</v>
       </c>
       <c r="E53" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G53" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H53">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="I53">
-        <v>65300</v>
+        <v>133</v>
       </c>
       <c r="J53" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="K53" t="s">
-        <v>51</v>
+        <v>354</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B54" t="s">
         <v>19</v>
       </c>
       <c r="C54" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D54" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E54" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F54" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G54" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H54">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="I54">
-        <v>65300</v>
+        <v>133</v>
       </c>
       <c r="J54" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B55" t="s">
         <v>19</v>
       </c>
       <c r="C55" t="s">
+        <v>363</v>
+      </c>
+      <c r="D55" t="s">
+        <v>364</v>
+      </c>
+      <c r="E55" t="s">
+        <v>64</v>
+      </c>
+      <c r="F55" t="s">
+        <v>65</v>
+      </c>
+      <c r="G55" t="s">
+        <v>66</v>
+      </c>
+      <c r="H55">
+        <v>14</v>
+      </c>
+      <c r="I55">
+        <v>179</v>
+      </c>
+      <c r="J55" t="s">
+        <v>365</v>
+      </c>
+      <c r="K55" t="s">
         <v>366</v>
-      </c>
-      <c r="D55" t="s">
-        <v>365</v>
-      </c>
-      <c r="E55" t="s">
-        <v>59</v>
-      </c>
-      <c r="F55" t="s">
-        <v>60</v>
-      </c>
-      <c r="G55" t="s">
-        <v>61</v>
-      </c>
-      <c r="H55">
-        <v>203</v>
-      </c>
-      <c r="I55">
-        <v>65300</v>
-      </c>
-      <c r="J55" t="s">
-        <v>357</v>
-      </c>
-      <c r="K55" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B56" t="s">
         <v>19</v>
@@ -3819,1253 +3729,728 @@
         <v>367</v>
       </c>
       <c r="D56" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E56" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F56" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G56" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H56">
-        <v>203</v>
+        <v>14</v>
       </c>
       <c r="I56">
-        <v>65300</v>
+        <v>179</v>
       </c>
       <c r="J56" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="K56" t="s">
-        <v>51</v>
+        <v>369</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="B57" t="s">
         <v>19</v>
       </c>
       <c r="C57" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D57" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="E57" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F57" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G57" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H57">
-        <v>203</v>
+        <v>14</v>
       </c>
       <c r="I57">
-        <v>65300</v>
+        <v>179</v>
       </c>
       <c r="J57" t="s">
-        <v>62</v>
+        <v>372</v>
       </c>
       <c r="K57" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B58" t="s">
         <v>19</v>
       </c>
       <c r="C58" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D58" t="s">
         <v>371</v>
       </c>
       <c r="E58" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F58" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G58" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H58">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I58">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="J58" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K58" t="s">
-        <v>25</v>
+        <v>376</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B59" t="s">
         <v>19</v>
       </c>
       <c r="C59" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D59" t="s">
-        <v>371</v>
+        <v>68</v>
       </c>
       <c r="E59" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F59" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G59" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H59">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I59">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="J59" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K59" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B60" t="s">
         <v>19</v>
       </c>
       <c r="C60" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D60" t="s">
-        <v>376</v>
+        <v>71</v>
       </c>
       <c r="E60" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F60" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G60" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H60">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I60">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="J60" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="K60" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B61" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="C61" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D61" t="s">
-        <v>376</v>
+        <v>90</v>
       </c>
       <c r="E61" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="F61" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="G61" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="H61">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I61">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J61" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="K61" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B62" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="C62" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="D62" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E62" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="F62" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="G62" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="H62">
-        <v>13</v>
+        <v>204</v>
       </c>
       <c r="I62">
-        <v>133</v>
+        <v>65301</v>
       </c>
       <c r="J62" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="K62" t="s">
-        <v>358</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B63" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="C63" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="D63" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E63" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="F63" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="G63" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="H63">
-        <v>13</v>
+        <v>204</v>
       </c>
       <c r="I63">
-        <v>133</v>
+        <v>65301</v>
       </c>
       <c r="J63" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="K63" t="s">
-        <v>25</v>
+        <v>391</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="B64" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="C64" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="D64" t="s">
-        <v>385</v>
+        <v>114</v>
       </c>
       <c r="E64" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="F64" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="G64" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="H64">
-        <v>13</v>
+        <v>204</v>
       </c>
       <c r="I64">
-        <v>133</v>
+        <v>65301</v>
       </c>
       <c r="J64" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="K64" t="s">
-        <v>378</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B65" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="C65" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="D65" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="E65" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="F65" t="s">
-        <v>69</v>
+        <v>118</v>
       </c>
       <c r="G65" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="H65">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I65">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="J65" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="K65" t="s">
-        <v>31</v>
+        <v>396</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B66" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="C66" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="D66" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="E66" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="F66" t="s">
-        <v>69</v>
+        <v>118</v>
       </c>
       <c r="G66" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="H66">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I66">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="J66" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="K66" t="s">
-        <v>358</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="B67" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="C67" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="D67" t="s">
-        <v>388</v>
+        <v>147</v>
       </c>
       <c r="E67" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="F67" t="s">
-        <v>69</v>
+        <v>149</v>
       </c>
       <c r="G67" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="H67">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="I67">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="J67" t="s">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="K67" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B68" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="C68" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="D68" t="s">
-        <v>391</v>
+        <v>154</v>
       </c>
       <c r="E68" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="F68" t="s">
-        <v>69</v>
+        <v>149</v>
       </c>
       <c r="G68" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="H68">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="I68">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="J68" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="K68" t="s">
-        <v>378</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="B69" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="C69" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="D69" t="s">
-        <v>391</v>
+        <v>157</v>
       </c>
       <c r="E69" t="s">
-        <v>68</v>
+        <v>158</v>
       </c>
       <c r="F69" t="s">
-        <v>69</v>
+        <v>159</v>
       </c>
       <c r="G69" t="s">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="H69">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="I69">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="J69" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="K69" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="C70" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="D70" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="E70" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="F70" t="s">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="G70" t="s">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="H70">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="I70">
-        <v>179</v>
+        <v>720</v>
       </c>
       <c r="J70" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="K70" t="s">
-        <v>396</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="B71" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="C71" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="D71" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="E71" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="F71" t="s">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="G71" t="s">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="H71">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="I71">
-        <v>179</v>
+        <v>720</v>
       </c>
       <c r="J71" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="K71" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="C72" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="D72" t="s">
-        <v>401</v>
+        <v>165</v>
       </c>
       <c r="E72" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="F72" t="s">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="G72" t="s">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="H72">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="I72">
-        <v>179</v>
+        <v>720</v>
       </c>
       <c r="J72" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="K72" t="s">
-        <v>403</v>
+        <v>343</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="C73" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="D73" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="E73" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="F73" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="G73" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="H73">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="I73">
-        <v>179</v>
+        <v>721</v>
       </c>
       <c r="J73" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="K73" t="s">
-        <v>406</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="C74" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="D74" t="s">
-        <v>76</v>
+        <v>414</v>
       </c>
       <c r="E74" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="F74" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="G74" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="H74">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="I74">
-        <v>179</v>
+        <v>721</v>
       </c>
       <c r="J74" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="K74" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="C75" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="D75" t="s">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="E75" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="F75" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="G75" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="H75">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="I75">
-        <v>179</v>
+        <v>721</v>
       </c>
       <c r="J75" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="K75" t="s">
-        <v>413</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="C76" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="D76" t="s">
-        <v>98</v>
+        <v>422</v>
       </c>
       <c r="E76" t="s">
-        <v>99</v>
+        <v>186</v>
       </c>
       <c r="F76" t="s">
-        <v>100</v>
+        <v>187</v>
       </c>
       <c r="G76" t="s">
-        <v>101</v>
+        <v>188</v>
       </c>
       <c r="H76">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I76">
-        <v>142</v>
+        <v>940</v>
       </c>
       <c r="J76" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="K76" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" t="s">
-        <v>82</v>
-      </c>
-      <c r="C77" t="s">
-        <v>416</v>
-      </c>
-      <c r="D77" t="s">
-        <v>417</v>
-      </c>
-      <c r="E77" t="s">
-        <v>118</v>
-      </c>
-      <c r="F77" t="s">
-        <v>119</v>
-      </c>
-      <c r="G77" t="s">
-        <v>120</v>
-      </c>
-      <c r="H77">
-        <v>204</v>
-      </c>
-      <c r="I77">
-        <v>65301</v>
-      </c>
-      <c r="J77" t="s">
-        <v>418</v>
-      </c>
-      <c r="K77" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78" t="s">
-        <v>82</v>
-      </c>
-      <c r="C78" t="s">
-        <v>419</v>
-      </c>
-      <c r="D78" t="s">
-        <v>417</v>
-      </c>
-      <c r="E78" t="s">
-        <v>118</v>
-      </c>
-      <c r="F78" t="s">
-        <v>119</v>
-      </c>
-      <c r="G78" t="s">
-        <v>120</v>
-      </c>
-      <c r="H78">
-        <v>204</v>
-      </c>
-      <c r="I78">
-        <v>65301</v>
-      </c>
-      <c r="J78" t="s">
-        <v>420</v>
-      </c>
-      <c r="K78" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" t="s">
-        <v>82</v>
-      </c>
-      <c r="C79" t="s">
-        <v>422</v>
-      </c>
-      <c r="D79" t="s">
-        <v>122</v>
-      </c>
-      <c r="E79" t="s">
-        <v>118</v>
-      </c>
-      <c r="F79" t="s">
-        <v>119</v>
-      </c>
-      <c r="G79" t="s">
-        <v>120</v>
-      </c>
-      <c r="H79">
-        <v>204</v>
-      </c>
-      <c r="I79">
-        <v>65301</v>
-      </c>
-      <c r="J79" t="s">
-        <v>418</v>
-      </c>
-      <c r="K79" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80" t="s">
-        <v>82</v>
-      </c>
-      <c r="C80" t="s">
-        <v>423</v>
-      </c>
-      <c r="D80" t="s">
         <v>424</v>
-      </c>
-      <c r="E80" t="s">
-        <v>125</v>
-      </c>
-      <c r="F80" t="s">
-        <v>126</v>
-      </c>
-      <c r="G80" t="s">
-        <v>127</v>
-      </c>
-      <c r="H80">
-        <v>18</v>
-      </c>
-      <c r="I80">
-        <v>141</v>
-      </c>
-      <c r="J80" t="s">
-        <v>425</v>
-      </c>
-      <c r="K80" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81" t="s">
-        <v>82</v>
-      </c>
-      <c r="C81" t="s">
-        <v>427</v>
-      </c>
-      <c r="D81" t="s">
-        <v>428</v>
-      </c>
-      <c r="E81" t="s">
-        <v>125</v>
-      </c>
-      <c r="F81" t="s">
-        <v>126</v>
-      </c>
-      <c r="G81" t="s">
-        <v>127</v>
-      </c>
-      <c r="H81">
-        <v>18</v>
-      </c>
-      <c r="I81">
-        <v>141</v>
-      </c>
-      <c r="J81" t="s">
-        <v>429</v>
-      </c>
-      <c r="K81" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82" t="s">
-        <v>153</v>
-      </c>
-      <c r="C82" t="s">
-        <v>430</v>
-      </c>
-      <c r="D82" t="s">
-        <v>155</v>
-      </c>
-      <c r="E82" t="s">
-        <v>156</v>
-      </c>
-      <c r="F82" t="s">
-        <v>157</v>
-      </c>
-      <c r="G82" t="s">
-        <v>158</v>
-      </c>
-      <c r="H82">
-        <v>24</v>
-      </c>
-      <c r="I82">
-        <v>170</v>
-      </c>
-      <c r="J82" t="s">
-        <v>431</v>
-      </c>
-      <c r="K82" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83" t="s">
-        <v>153</v>
-      </c>
-      <c r="C83" t="s">
-        <v>432</v>
-      </c>
-      <c r="D83" t="s">
-        <v>162</v>
-      </c>
-      <c r="E83" t="s">
-        <v>156</v>
-      </c>
-      <c r="F83" t="s">
-        <v>157</v>
-      </c>
-      <c r="G83" t="s">
-        <v>158</v>
-      </c>
-      <c r="H83">
-        <v>24</v>
-      </c>
-      <c r="I83">
-        <v>170</v>
-      </c>
-      <c r="J83" t="s">
-        <v>431</v>
-      </c>
-      <c r="K83" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84" t="s">
-        <v>153</v>
-      </c>
-      <c r="C84" t="s">
-        <v>433</v>
-      </c>
-      <c r="D84" t="s">
-        <v>165</v>
-      </c>
-      <c r="E84" t="s">
-        <v>166</v>
-      </c>
-      <c r="F84" t="s">
-        <v>167</v>
-      </c>
-      <c r="G84" t="s">
-        <v>168</v>
-      </c>
-      <c r="H84">
-        <v>46</v>
-      </c>
-      <c r="I84">
-        <v>171</v>
-      </c>
-      <c r="J84" t="s">
-        <v>434</v>
-      </c>
-      <c r="K84" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="s">
-        <v>171</v>
-      </c>
-      <c r="C85" t="s">
-        <v>435</v>
-      </c>
-      <c r="D85" t="s">
-        <v>436</v>
-      </c>
-      <c r="E85" t="s">
-        <v>174</v>
-      </c>
-      <c r="F85" t="s">
-        <v>175</v>
-      </c>
-      <c r="G85" t="s">
-        <v>176</v>
-      </c>
-      <c r="H85">
-        <v>59</v>
-      </c>
-      <c r="I85">
-        <v>720</v>
-      </c>
-      <c r="J85" t="s">
-        <v>437</v>
-      </c>
-      <c r="K85" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86" t="s">
-        <v>171</v>
-      </c>
-      <c r="C86" t="s">
-        <v>438</v>
-      </c>
-      <c r="D86" t="s">
-        <v>436</v>
-      </c>
-      <c r="E86" t="s">
-        <v>174</v>
-      </c>
-      <c r="F86" t="s">
-        <v>175</v>
-      </c>
-      <c r="G86" t="s">
-        <v>176</v>
-      </c>
-      <c r="H86">
-        <v>59</v>
-      </c>
-      <c r="I86">
-        <v>720</v>
-      </c>
-      <c r="J86" t="s">
-        <v>439</v>
-      </c>
-      <c r="K86" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>86</v>
-      </c>
-      <c r="B87" t="s">
-        <v>171</v>
-      </c>
-      <c r="C87" t="s">
-        <v>441</v>
-      </c>
-      <c r="D87" t="s">
-        <v>173</v>
-      </c>
-      <c r="E87" t="s">
-        <v>174</v>
-      </c>
-      <c r="F87" t="s">
-        <v>175</v>
-      </c>
-      <c r="G87" t="s">
-        <v>176</v>
-      </c>
-      <c r="H87">
-        <v>59</v>
-      </c>
-      <c r="I87">
-        <v>720</v>
-      </c>
-      <c r="J87" t="s">
-        <v>442</v>
-      </c>
-      <c r="K87" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88" t="s">
-        <v>171</v>
-      </c>
-      <c r="C88" t="s">
-        <v>443</v>
-      </c>
-      <c r="D88" t="s">
-        <v>444</v>
-      </c>
-      <c r="E88" t="s">
-        <v>181</v>
-      </c>
-      <c r="F88" t="s">
-        <v>182</v>
-      </c>
-      <c r="G88" t="s">
-        <v>183</v>
-      </c>
-      <c r="H88">
-        <v>60</v>
-      </c>
-      <c r="I88">
-        <v>721</v>
-      </c>
-      <c r="J88" t="s">
-        <v>445</v>
-      </c>
-      <c r="K88" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>88</v>
-      </c>
-      <c r="B89" t="s">
-        <v>171</v>
-      </c>
-      <c r="C89" t="s">
-        <v>446</v>
-      </c>
-      <c r="D89" t="s">
-        <v>444</v>
-      </c>
-      <c r="E89" t="s">
-        <v>181</v>
-      </c>
-      <c r="F89" t="s">
-        <v>182</v>
-      </c>
-      <c r="G89" t="s">
-        <v>183</v>
-      </c>
-      <c r="H89">
-        <v>60</v>
-      </c>
-      <c r="I89">
-        <v>721</v>
-      </c>
-      <c r="J89" t="s">
-        <v>447</v>
-      </c>
-      <c r="K89" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>89</v>
-      </c>
-      <c r="B90" t="s">
-        <v>171</v>
-      </c>
-      <c r="C90" t="s">
-        <v>449</v>
-      </c>
-      <c r="D90" t="s">
-        <v>180</v>
-      </c>
-      <c r="E90" t="s">
-        <v>181</v>
-      </c>
-      <c r="F90" t="s">
-        <v>182</v>
-      </c>
-      <c r="G90" t="s">
-        <v>183</v>
-      </c>
-      <c r="H90">
-        <v>60</v>
-      </c>
-      <c r="I90">
-        <v>721</v>
-      </c>
-      <c r="J90" t="s">
-        <v>450</v>
-      </c>
-      <c r="K90" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>90</v>
-      </c>
-      <c r="B91" t="s">
-        <v>171</v>
-      </c>
-      <c r="C91" t="s">
-        <v>451</v>
-      </c>
-      <c r="D91" t="s">
-        <v>452</v>
-      </c>
-      <c r="E91" t="s">
-        <v>194</v>
-      </c>
-      <c r="F91" t="s">
-        <v>195</v>
-      </c>
-      <c r="G91" t="s">
-        <v>196</v>
-      </c>
-      <c r="H91">
-        <v>67</v>
-      </c>
-      <c r="I91">
-        <v>940</v>
-      </c>
-      <c r="J91" t="s">
-        <v>453</v>
-      </c>
-      <c r="K91" t="s">
-        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -5084,10 +4469,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -5095,7 +4480,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -5103,7 +4488,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -5111,7 +4496,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -5119,7 +4504,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -5127,7 +4512,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -5135,7 +4520,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -5143,7 +4528,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5151,7 +4536,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -5159,7 +4544,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -5167,7 +4552,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -5175,7 +4560,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -5184,240 +4569,240 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B14" s="10"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -5426,7 +4811,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B45" s="10"/>
     </row>
@@ -5435,7 +4820,7 @@
         <v>1</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -5443,7 +4828,7 @@
         <v>2</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -5451,7 +4836,7 @@
         <v>3</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -5459,7 +4844,7 @@
         <v>4</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>

--- a/Form-Layout/ImportLayouts/Config/RPT_Import_Map.xlsx
+++ b/Form-Layout/ImportLayouts/Config/RPT_Import_Map.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SBO_Warit\Form-Layout\ImportLayouts\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\SDAWR\WARIT\SBO_Warit\Form-Layout\ImportLayouts\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87787DE-2E36-46E3-A08B-E61C1993F1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC13738-832E-4B55-B011-67414213E28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{014D90F8-196E-40BF-BFE8-06F39FDF4BE1}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="426">
   <si>
     <t>No</t>
   </si>
@@ -1312,17 +1312,20 @@
   </si>
   <si>
     <t>Inventory Transfer_ใบโอนสินค้า</t>
+  </si>
+  <si>
+    <t>Default</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -1331,7 +1334,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1339,7 +1342,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1347,7 +1350,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1355,7 +1358,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF8000"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1779,8 +1782,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F62795C-81CC-4DF6-8643-8C6776741771}">
-  <dimension ref="A1:K76"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L76"/>
+  <sheetFormatPr defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="5.69921875" customWidth="1"/>
     <col min="2" max="2" width="14.69921875" customWidth="1"/>
@@ -1791,9 +1794,10 @@
     <col min="9" max="9" width="14.69921875" customWidth="1"/>
     <col min="10" max="10" width="28.69921875" customWidth="1"/>
     <col min="11" max="11" width="22.69921875" customWidth="1"/>
+    <col min="12" max="12" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="30" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1827,8 +1831,11 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -1863,7 +1870,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="33.6">
       <c r="A3" s="12">
         <v>4</v>
       </c>
@@ -1898,7 +1905,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="33.6">
       <c r="A4" s="11">
         <v>5</v>
       </c>
@@ -1933,7 +1940,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12">
       <c r="A5" s="12">
         <v>6</v>
       </c>
@@ -1968,7 +1975,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12">
       <c r="A6" s="12">
         <v>8</v>
       </c>
@@ -2003,7 +2010,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12">
       <c r="A7" s="11">
         <v>9</v>
       </c>
@@ -2038,7 +2045,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12">
       <c r="A8" s="12">
         <v>10</v>
       </c>
@@ -2073,7 +2080,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="33.6">
       <c r="A9" s="11">
         <v>11</v>
       </c>
@@ -2108,7 +2115,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="33.6">
       <c r="A10" s="12">
         <v>12</v>
       </c>
@@ -2143,7 +2150,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="33.6">
       <c r="A11" s="12">
         <v>13</v>
       </c>
@@ -2178,7 +2185,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="33.6">
       <c r="A12" s="11">
         <v>14</v>
       </c>
@@ -2213,7 +2220,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="33.6">
       <c r="A13" s="12">
         <v>15</v>
       </c>
@@ -2248,7 +2255,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="33.6">
       <c r="A14" s="12">
         <v>16</v>
       </c>
@@ -2283,7 +2290,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12">
       <c r="A15" s="11">
         <v>17</v>
       </c>
@@ -2318,7 +2325,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="33.6">
       <c r="A16" s="12">
         <v>18</v>
       </c>
@@ -2353,7 +2360,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="33.6">
       <c r="A17" s="12">
         <v>19</v>
       </c>
@@ -2388,7 +2395,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="33.6">
       <c r="A18" s="11">
         <v>20</v>
       </c>
@@ -2423,7 +2430,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="33.6">
       <c r="A19" s="12">
         <v>21</v>
       </c>
@@ -2458,7 +2465,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="33.6">
       <c r="A20" s="12">
         <v>22</v>
       </c>
@@ -2493,7 +2500,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11">
       <c r="A21" s="11">
         <v>23</v>
       </c>
@@ -2528,7 +2535,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11">
       <c r="A22" s="12">
         <v>24</v>
       </c>
@@ -2563,7 +2570,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="33.6">
       <c r="A23" s="12">
         <v>25</v>
       </c>
@@ -2598,7 +2605,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="33.6">
       <c r="A24" s="11">
         <v>26</v>
       </c>
@@ -2633,7 +2640,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="33.6">
       <c r="A25" s="12">
         <v>27</v>
       </c>
@@ -2668,7 +2675,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11">
       <c r="A26" s="12">
         <v>28</v>
       </c>
@@ -2703,7 +2710,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="33.6">
       <c r="A27" s="11">
         <v>29</v>
       </c>
@@ -2738,7 +2745,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11">
       <c r="A28" s="12">
         <v>30</v>
       </c>
@@ -2773,7 +2780,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="33.6">
       <c r="A29" s="12">
         <v>31</v>
       </c>
@@ -2808,7 +2815,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="33.6">
       <c r="A30" s="11">
         <v>32</v>
       </c>
@@ -2843,7 +2850,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="33.6">
       <c r="A31" s="12">
         <v>33</v>
       </c>
@@ -2878,7 +2885,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="33.6">
       <c r="A32" s="12">
         <v>34</v>
       </c>
@@ -2913,7 +2920,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="33.6">
       <c r="A33" s="11">
         <v>35</v>
       </c>
@@ -2948,7 +2955,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="33.6">
       <c r="A34" s="12">
         <v>36</v>
       </c>
@@ -2983,7 +2990,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11">
       <c r="A35" s="12">
         <v>37</v>
       </c>
@@ -3018,7 +3025,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" ht="33.6">
       <c r="A36" s="11">
         <v>38</v>
       </c>
@@ -3053,7 +3060,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="33.6">
       <c r="A37" s="12">
         <v>39</v>
       </c>
@@ -3088,7 +3095,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" ht="33.6">
       <c r="A38" s="12">
         <v>40</v>
       </c>
@@ -3123,7 +3130,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="33.6">
       <c r="A39" s="11">
         <v>41</v>
       </c>
@@ -3158,7 +3165,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11">
       <c r="A40" s="12">
         <v>42</v>
       </c>
@@ -3193,7 +3200,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11">
       <c r="A41" s="12">
         <v>43</v>
       </c>
@@ -3228,7 +3235,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11">
       <c r="A42" s="11">
         <v>44</v>
       </c>
@@ -3263,7 +3270,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11">
       <c r="A43" s="12">
         <v>45</v>
       </c>
@@ -3298,7 +3305,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11">
       <c r="A44">
         <v>46</v>
       </c>
@@ -3333,7 +3340,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11">
       <c r="A45">
         <v>49</v>
       </c>
@@ -3368,7 +3375,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11">
       <c r="A46">
         <v>52</v>
       </c>
@@ -3403,7 +3410,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11">
       <c r="A47">
         <v>55</v>
       </c>
@@ -3438,7 +3445,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11">
       <c r="A48">
         <v>56</v>
       </c>
@@ -3473,7 +3480,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11">
       <c r="A49">
         <v>59</v>
       </c>
@@ -3508,7 +3515,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11">
       <c r="A50">
         <v>60</v>
       </c>
@@ -3543,7 +3550,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11">
       <c r="A51">
         <v>63</v>
       </c>
@@ -3578,7 +3585,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11">
       <c r="A52">
         <v>64</v>
       </c>
@@ -3613,7 +3620,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11">
       <c r="A53">
         <v>67</v>
       </c>
@@ -3648,7 +3655,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11">
       <c r="A54">
         <v>68</v>
       </c>
@@ -3683,7 +3690,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11">
       <c r="A55">
         <v>69</v>
       </c>
@@ -3718,7 +3725,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11">
       <c r="A56">
         <v>70</v>
       </c>
@@ -3753,7 +3760,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11">
       <c r="A57">
         <v>71</v>
       </c>
@@ -3788,7 +3795,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11">
       <c r="A58">
         <v>72</v>
       </c>
@@ -3823,7 +3830,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11">
       <c r="A59">
         <v>73</v>
       </c>
@@ -3858,7 +3865,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11">
       <c r="A60">
         <v>74</v>
       </c>
@@ -3893,7 +3900,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11">
       <c r="A61">
         <v>75</v>
       </c>
@@ -3928,7 +3935,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11">
       <c r="A62">
         <v>76</v>
       </c>
@@ -3963,7 +3970,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11">
       <c r="A63">
         <v>77</v>
       </c>
@@ -3998,7 +4005,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11">
       <c r="A64">
         <v>78</v>
       </c>
@@ -4033,7 +4040,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11">
       <c r="A65">
         <v>79</v>
       </c>
@@ -4068,7 +4075,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11">
       <c r="A66">
         <v>80</v>
       </c>
@@ -4103,7 +4110,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11">
       <c r="A67">
         <v>81</v>
       </c>
@@ -4138,7 +4145,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11">
       <c r="A68">
         <v>82</v>
       </c>
@@ -4173,7 +4180,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11">
       <c r="A69">
         <v>83</v>
       </c>
@@ -4208,7 +4215,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11">
       <c r="A70">
         <v>84</v>
       </c>
@@ -4243,7 +4250,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11">
       <c r="A71">
         <v>85</v>
       </c>
@@ -4278,7 +4285,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11">
       <c r="A72">
         <v>86</v>
       </c>
@@ -4313,7 +4320,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11">
       <c r="A73">
         <v>87</v>
       </c>
@@ -4348,7 +4355,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11">
       <c r="A74">
         <v>88</v>
       </c>
@@ -4383,7 +4390,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11">
       <c r="A75">
         <v>89</v>
       </c>
@@ -4418,7 +4425,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11">
       <c r="A76">
         <v>90</v>
       </c>
@@ -4461,13 +4468,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F598BE85-BEA9-4F93-8400-E7BAEF1B0041}">
   <dimension ref="A1:B49"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="24.69921875" customWidth="1"/>
     <col min="2" max="2" width="65.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="9" t="s">
         <v>264</v>
       </c>
@@ -4475,7 +4482,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4483,7 +4490,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -4491,7 +4498,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -4499,7 +4506,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -4507,7 +4514,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -4515,7 +4522,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -4523,7 +4530,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -4531,7 +4538,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -4539,7 +4546,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -4547,7 +4554,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -4555,7 +4562,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -4563,17 +4570,17 @@
         <v>276</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" s="10" t="s">
         <v>277</v>
       </c>
       <c r="B14" s="10"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
         <v>278</v>
       </c>
@@ -4581,7 +4588,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
         <v>280</v>
       </c>
@@ -4589,7 +4596,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
         <v>282</v>
       </c>
@@ -4597,7 +4604,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
         <v>284</v>
       </c>
@@ -4605,7 +4612,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
         <v>286</v>
       </c>
@@ -4613,7 +4620,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
         <v>288</v>
       </c>
@@ -4621,7 +4628,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
         <v>290</v>
       </c>
@@ -4629,7 +4636,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
         <v>292</v>
       </c>
@@ -4637,7 +4644,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
         <v>294</v>
       </c>
@@ -4645,7 +4652,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
         <v>296</v>
       </c>
@@ -4653,7 +4660,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
         <v>298</v>
       </c>
@@ -4661,7 +4668,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
         <v>300</v>
       </c>
@@ -4669,7 +4676,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
         <v>302</v>
       </c>
@@ -4677,7 +4684,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
         <v>304</v>
       </c>
@@ -4685,7 +4692,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
         <v>306</v>
       </c>
@@ -4693,7 +4700,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
         <v>308</v>
       </c>
@@ -4701,7 +4708,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
         <v>310</v>
       </c>
@@ -4709,7 +4716,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
         <v>312</v>
       </c>
@@ -4717,7 +4724,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
         <v>314</v>
       </c>
@@ -4725,7 +4732,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
         <v>316</v>
       </c>
@@ -4733,7 +4740,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
         <v>318</v>
       </c>
@@ -4741,7 +4748,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
         <v>320</v>
       </c>
@@ -4749,7 +4756,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
         <v>322</v>
       </c>
@@ -4757,7 +4764,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
         <v>324</v>
       </c>
@@ -4765,7 +4772,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
         <v>326</v>
       </c>
@@ -4773,7 +4780,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
         <v>328</v>
       </c>
@@ -4781,7 +4788,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
         <v>243</v>
       </c>
@@ -4789,7 +4796,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
         <v>261</v>
       </c>
@@ -4797,7 +4804,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
         <v>255</v>
       </c>
@@ -4805,17 +4812,17 @@
         <v>332</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2">
       <c r="A45" s="10" t="s">
         <v>333</v>
       </c>
       <c r="B45" s="10"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2">
       <c r="A46" s="1">
         <v>1</v>
       </c>
@@ -4823,7 +4830,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2">
       <c r="A47" s="1">
         <v>2</v>
       </c>
@@ -4831,7 +4838,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2">
       <c r="A48" s="1">
         <v>3</v>
       </c>
@@ -4839,7 +4846,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2">
       <c r="A49" s="1">
         <v>4</v>
       </c>
